--- a/docs/d/211/inyear.xlsx
+++ b/docs/d/211/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 70 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 68 clubs short</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3040,8 +3040,8 @@
       <c r="Y24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z24" s="9" t="n">
-        <v>0</v>
+      <c r="Z24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA24" s="10" t="n">
         <v>1</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8357,8 +8357,8 @@
       <c r="S79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T79" s="9" t="n">
-        <v>0</v>
+      <c r="T79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U79" s="9" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
@@ -8557,8 +8557,8 @@
       <c r="U81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V81" s="9" t="n">
-        <v>3</v>
+      <c r="V81" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -9830,8 +9830,8 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="10" t="n">
         <v>1</v>
@@ -13452,7 +13452,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -13848,7 +13848,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13947,7 +13947,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>

--- a/docs/d/211/inyear.xlsx
+++ b/docs/d/211/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/211/inyear.xlsx
+++ b/docs/d/211/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 68 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 64 clubs short</t>
         </is>
       </c>
     </row>
@@ -1579,8 +1579,8 @@
       <c r="W9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X9" s="9" t="n">
-        <v>3</v>
+      <c r="X9" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y9" s="9" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2065,13 +2065,13 @@
         <v>0</v>
       </c>
       <c r="X14" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -5730,7 +5730,7 @@
         <v>0</v>
       </c>
       <c r="Q52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" s="9" t="n">
         <v>0</v>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>4</v>
       </c>
       <c r="W81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X81" s="10" t="n">
         <v>5</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -8739,8 +8739,8 @@
       <c r="Q83" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R83" s="9" t="n">
-        <v>1</v>
+      <c r="R83" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S83" s="9" t="n">
         <v>0</v>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10121,8 +10121,8 @@
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -10342,7 +10342,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10412,8 +10412,8 @@
       <c r="Y100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" s="9" t="n">
-        <v>0</v>
+      <c r="Z100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA100" s="10" t="n">
         <v>1</v>
@@ -11667,8 +11667,8 @@
       <c r="W113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X113" s="9" t="n">
-        <v>3</v>
+      <c r="X113" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12061,8 +12061,8 @@
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="9" t="n">
-        <v>0</v>
+      <c r="Z117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
@@ -12347,7 +12347,7 @@
         <v>0</v>
       </c>
       <c r="X120" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
@@ -13386,7 +13386,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -13881,7 +13881,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13980,7 +13980,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14112,7 +14112,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>

--- a/docs/d/211/inyear.xlsx
+++ b/docs/d/211/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 64 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 36 clubs short</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1373,8 +1373,8 @@
       <c r="S7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T7" s="9" t="n">
-        <v>0</v>
+      <c r="T7" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U7" s="9" t="n">
         <v>0</v>
@@ -1876,8 +1876,8 @@
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="9" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2264,8 +2264,8 @@
       <c r="Y16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="9" t="n">
-        <v>0</v>
+      <c r="Z16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA16" s="10" t="n">
         <v>1</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2361,8 +2361,8 @@
       <c r="Y17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" s="9" t="n">
-        <v>0</v>
+      <c r="Z17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA17" s="10" t="n">
         <v>1</v>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2440,8 +2440,8 @@
       <c r="S18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T18" s="9" t="n">
-        <v>0</v>
+      <c r="T18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U18" s="9" t="n">
         <v>0</v>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2555,8 +2555,8 @@
       <c r="Y19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z19" s="9" t="n">
-        <v>0</v>
+      <c r="Z19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA19" s="10" t="n">
         <v>1</v>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2820,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="9" t="n">
         <v>0</v>
@@ -2828,8 +2828,8 @@
       <c r="S22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T22" s="9" t="n">
-        <v>0</v>
+      <c r="T22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U22" s="9" t="n">
         <v>0</v>
@@ -2846,8 +2846,8 @@
       <c r="Y22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="9" t="n">
-        <v>0</v>
+      <c r="Z22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA22" s="10" t="n">
         <v>1</v>
@@ -2943,8 +2943,8 @@
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="9" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3234,8 +3234,8 @@
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="n">
-        <v>0</v>
+      <c r="Z26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="10" t="n">
         <v>1</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3331,8 +3331,8 @@
       <c r="Y27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="9" t="n">
-        <v>0</v>
+      <c r="Z27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="10" t="n">
         <v>1</v>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4592,8 +4592,8 @@
       <c r="Y40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z40" s="9" t="n">
-        <v>0</v>
+      <c r="Z40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA40" s="10" t="n">
         <v>1</v>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="X42" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y42" s="9" t="n">
         <v>0</v>
@@ -4857,7 +4857,7 @@
         <v>0</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" s="9" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5174,8 +5174,8 @@
       <c r="Y46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z46" s="9" t="n">
-        <v>0</v>
+      <c r="Z46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA46" s="10" t="n">
         <v>1</v>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5562,8 +5562,8 @@
       <c r="Y50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" s="9" t="n">
-        <v>0</v>
+      <c r="Z50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA50" s="10" t="n">
         <v>1</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5659,8 +5659,8 @@
       <c r="Y51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="9" t="n">
-        <v>0</v>
+      <c r="Z51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" s="10" t="n">
         <v>1</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -5853,8 +5853,8 @@
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="9" t="n">
-        <v>0</v>
+      <c r="Z53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -5950,8 +5950,8 @@
       <c r="Y54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z54" s="9" t="n">
-        <v>0</v>
+      <c r="Z54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA54" s="10" t="n">
         <v>1</v>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6435,8 +6435,8 @@
       <c r="Y59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="9" t="n">
-        <v>0</v>
+      <c r="Z59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA59" s="10" t="n">
         <v>1</v>
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6629,8 +6629,8 @@
       <c r="Y61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z61" s="9" t="n">
-        <v>0</v>
+      <c r="Z61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA61" s="10" t="n">
         <v>1</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7017,8 +7017,8 @@
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7405,8 +7405,8 @@
       <c r="Y69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" s="9" t="n">
-        <v>0</v>
+      <c r="Z69" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA69" s="10" t="n">
         <v>1</v>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -7793,8 +7793,8 @@
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="9" t="n">
-        <v>0</v>
+      <c r="Z73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA73" s="10" t="n">
         <v>1</v>
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8084,8 +8084,8 @@
       <c r="Y76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z76" s="9" t="n">
-        <v>0</v>
+      <c r="Z76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA76" s="10" t="n">
         <v>1</v>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8181,8 +8181,8 @@
       <c r="Y77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z77" s="9" t="n">
-        <v>0</v>
+      <c r="Z77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA77" s="10" t="n">
         <v>1</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8666,8 +8666,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -8860,8 +8860,8 @@
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="9" t="n">
-        <v>0</v>
+      <c r="Z84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA84" s="10" t="n">
         <v>1</v>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10994,8 +10994,8 @@
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
@@ -11570,8 +11570,8 @@
       <c r="W112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X112" s="9" t="n">
-        <v>0</v>
+      <c r="X112" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11673,8 +11673,8 @@
       <c r="Y113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z113" s="9" t="n">
-        <v>0</v>
+      <c r="Z113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA113" s="10" t="n">
         <v>1</v>
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>0</v>
       </c>
       <c r="V121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12546,8 +12546,8 @@
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="9" t="n">
-        <v>0</v>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
@@ -12670,7 +12670,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12740,8 +12740,8 @@
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="9" t="n">
-        <v>0</v>
+      <c r="Z124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12837,8 +12837,8 @@
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="9" t="n">
-        <v>0</v>
+      <c r="Z125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
@@ -13353,7 +13353,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -13386,7 +13386,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -13452,7 +13452,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -13485,7 +13485,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -13551,7 +13551,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -13584,7 +13584,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -13617,7 +13617,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13650,7 +13650,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -13683,7 +13683,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13716,7 +13716,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13749,7 +13749,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13782,7 +13782,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13815,7 +13815,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13848,7 +13848,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13881,7 +13881,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -14013,7 +14013,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14079,7 +14079,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -14145,7 +14145,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>

--- a/docs/d/211/inyear.xlsx
+++ b/docs/d/211/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$130</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 36 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 36 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA129"/>
+  <dimension ref="A1:AA130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2014,17 +2014,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M14" s="8" t="n">
@@ -2062,7 +2062,7 @@
         <v>4</v>
       </c>
       <c r="W14" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>5</v>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>2</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="9" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
         <v>1</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3119,8 +3119,8 @@
       <c r="S25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T25" s="9" t="n">
-        <v>0</v>
+      <c r="T25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U25" s="9" t="n">
         <v>0</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>1</v>
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>1</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" s="9" t="n">
         <v>0</v>
@@ -3857,17 +3857,17 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-21</v>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M33" s="8" t="n">
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" s="9" t="n">
         <v>0</v>
@@ -3998,11 +3998,11 @@
       <c r="U34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="9" t="n">
-        <v>3</v>
+      <c r="V34" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>5</v>
@@ -4051,17 +4051,17 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M35" s="8" t="n">
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4483,8 +4483,8 @@
       <c r="U39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V39" s="9" t="n">
-        <v>3</v>
+      <c r="V39" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -4827,17 +4827,17 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M43" s="8" t="n">
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5118,17 +5118,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M46" s="8" t="n">
@@ -5163,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>4</v>
       </c>
       <c r="W49" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X49" s="10" t="n">
         <v>5</v>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5700,17 +5700,17 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M52" s="8" t="n">
@@ -5745,7 +5745,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W52" s="9" t="n">
         <v>0</v>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6088,17 +6088,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="8" t="n">
@@ -6185,17 +6185,17 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M57" s="8" t="n">
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6476,17 +6476,17 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M60" s="8" t="n">
@@ -6573,17 +6573,17 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M61" s="8" t="n">
@@ -6648,15 +6648,15 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>7936</v>
+        <v>4587</v>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Fireside Toastmasters Club</t>
+          <t>Effingham Toastmasters</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -6670,25 +6670,25 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>9</v>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M62" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O62" s="7" t="inlineStr">
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c r="P62" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="9" t="n">
         <v>0</v>
@@ -6714,23 +6714,23 @@
       <c r="U62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" s="10" t="n">
+      <c r="V62" s="10" t="n">
         <v>4</v>
       </c>
+      <c r="W62" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="X62" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="Y62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" s="10" t="n">
-        <v>1</v>
+      <c r="Z62" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA62" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -6745,15 +6745,15 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>467</v>
+        <v>7936</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>McKinley Club</t>
+          <t>Fireside Toastmasters Club</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="P63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" s="9" t="n">
         <v>0</v>
@@ -6811,20 +6811,20 @@
       <c r="U63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="10" t="n">
+      <c r="V63" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="10" t="n">
-        <v>1</v>
+      <c r="Z63" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
@@ -6842,15 +6842,15 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>1351517</v>
+        <v>467</v>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>The Leadership Train</t>
+          <t>McKinley Club</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -6908,20 +6908,20 @@
       <c r="U64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V64" s="9" t="n">
-        <v>0</v>
+      <c r="V64" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" s="10" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="X64" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="9" t="n">
-        <v>0</v>
+      <c r="Z64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA64" s="10" t="n">
         <v>1</v>
@@ -6939,15 +6939,15 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>7423</v>
+        <v>1351517</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Toast of Champaign Club</t>
+          <t>The Leadership Train</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q65" s="9" t="n">
         <v>0</v>
@@ -6999,26 +6999,26 @@
       <c r="S65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T65" s="10" t="n">
-        <v>1</v>
+      <c r="T65" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X65" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="10" t="n">
-        <v>1</v>
+      <c r="Z65" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -7032,19 +7032,19 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>1313356</v>
+        <v>7423</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Capital City Toastmasters</t>
+          <t>Toast of Champaign Club</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>1</v>
       </c>
       <c r="Q66" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66" s="9" t="n">
         <v>0</v>
@@ -7096,20 +7096,20 @@
       <c r="S66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T66" s="9" t="n">
-        <v>0</v>
+      <c r="T66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X66" s="9" t="n">
-        <v>3</v>
+      <c r="X66" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y66" s="9" t="n">
         <v>0</v>
@@ -7133,15 +7133,15 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>1130739</v>
+        <v>1313356</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Gem City Toastmasters</t>
+          <t>Capital City Toastmasters</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="P67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" s="9" t="n">
         <v>0</v>
@@ -7193,8 +7193,8 @@
       <c r="S67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T67" s="10" t="n">
-        <v>1</v>
+      <c r="T67" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U67" s="9" t="n">
         <v>0</v>
@@ -7205,8 +7205,8 @@
       <c r="W67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X67" s="10" t="n">
-        <v>5</v>
+      <c r="X67" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y67" s="9" t="n">
         <v>0</v>
@@ -7230,15 +7230,15 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>1478393</v>
+        <v>1130739</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Horace Mann Toastmasters</t>
+          <t>Gem City Toastmasters</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="P68" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q68" s="9" t="n">
         <v>0</v>
@@ -7290,8 +7290,8 @@
       <c r="S68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T68" s="9" t="n">
-        <v>0</v>
+      <c r="T68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U68" s="9" t="n">
         <v>0</v>
@@ -7308,8 +7308,8 @@
       <c r="Y68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z68" s="9" t="n">
-        <v>0</v>
+      <c r="Z68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA68" s="10" t="n">
         <v>1</v>
@@ -7327,15 +7327,15 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>51</v>
+        <v>1478393</v>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>McBrian Lincoln-Douglas Club</t>
+          <t>Horace Mann Toastmasters</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>1</v>
       </c>
       <c r="Q69" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69" s="9" t="n">
         <v>0</v>
@@ -7394,19 +7394,19 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X69" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" s="10" t="n">
-        <v>1</v>
+      <c r="Z69" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA69" s="10" t="n">
         <v>1</v>
@@ -7424,11 +7424,11 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>7316</v>
+        <v>51</v>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Noontime Toastmasters Club</t>
+          <t>McBrian Lincoln-Douglas Club</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>1</v>
       </c>
       <c r="Q70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" s="9" t="n">
         <v>0</v>
@@ -7491,13 +7491,13 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X70" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y70" s="9" t="n">
         <v>0</v>
@@ -7517,15 +7517,15 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>7047091</v>
+        <v>7316</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Mount Vernon Toastmasters</t>
+          <t>Noontime Toastmasters Club</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         </is>
       </c>
       <c r="P71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q71" s="9" t="n">
         <v>0</v>
@@ -7588,13 +7588,13 @@
         <v>0</v>
       </c>
       <c r="V71" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X71" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y71" s="9" t="n">
         <v>0</v>
@@ -7618,15 +7618,15 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>9793</v>
+        <v>7047091</v>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Scott Speakers Association</t>
+          <t>Mount Vernon Toastmasters</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -7685,19 +7685,19 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X72" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
@@ -7715,15 +7715,15 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>606012</v>
+        <v>9793</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Southern Illinois Toastmasters Club</t>
+          <t>Scott Speakers Association</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -7737,17 +7737,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M73" s="8" t="n">
@@ -7775,26 +7775,26 @@
       <c r="S73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T73" s="10" t="n">
-        <v>1</v>
+      <c r="T73" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X73" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="10" t="n">
-        <v>1</v>
+      <c r="Z73" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA73" s="10" t="n">
         <v>1</v>
@@ -7812,15 +7812,15 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>3345884</v>
+        <v>606012</v>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Top Talk Toastmasters!</t>
+          <t>Southern Illinois Toastmasters Club</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -7872,26 +7872,26 @@
       <c r="S74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T74" s="9" t="n">
-        <v>0</v>
+      <c r="T74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X74" s="9" t="n">
-        <v>0</v>
+      <c r="X74" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" s="9" t="n">
-        <v>0</v>
+      <c r="Z74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA74" s="10" t="n">
         <v>1</v>
@@ -7905,19 +7905,19 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>4129</v>
+        <v>3345884</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Collinsville Toastmasters Club</t>
+          <t>Top Talk Toastmasters!</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -7960,35 +7960,35 @@
       <c r="P75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" s="10" t="n">
-        <v>2</v>
+      <c r="Q75" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S75" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T75" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T75" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X75" s="10" t="n">
-        <v>5</v>
+      <c r="X75" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z75" s="10" t="n">
-        <v>1</v>
+      <c r="Z75" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA75" s="10" t="n">
         <v>1</v>
@@ -8006,15 +8006,15 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>994</v>
+        <v>4129</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>O'Fallon Toastmasters</t>
+          <t>Collinsville Toastmasters Club</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8057,23 +8057,23 @@
       <c r="P76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" s="9" t="n">
-        <v>0</v>
+      <c r="Q76" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8103,15 +8103,15 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>496</v>
+        <v>994</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>St Clair Toastmasters</t>
+          <t>O'Fallon Toastmasters</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         </is>
       </c>
       <c r="P77" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q77" s="9" t="n">
         <v>0</v>
@@ -8163,8 +8163,8 @@
       <c r="S77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T77" s="10" t="n">
-        <v>1</v>
+      <c r="T77" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U77" s="9" t="n">
         <v>0</v>
@@ -8176,7 +8176,7 @@
         <v>0</v>
       </c>
       <c r="X77" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y77" s="9" t="n">
         <v>0</v>
@@ -8200,11 +8200,11 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>2967717</v>
+        <v>496</v>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Toast of Belleville</t>
+          <t>St Clair Toastmasters</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         </is>
       </c>
       <c r="P78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q78" s="9" t="n">
         <v>0</v>
@@ -8273,7 +8273,7 @@
         <v>0</v>
       </c>
       <c r="X78" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y78" s="9" t="n">
         <v>0</v>
@@ -8288,24 +8288,24 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>3273397</v>
+        <v>2967717</v>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Alpha Toastmasters</t>
+          <t>Toast of Belleville</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8319,13 +8319,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8364,19 +8364,19 @@
         <v>0</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X79" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA79" s="10" t="n">
         <v>1</v>
@@ -8394,11 +8394,11 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>503</v>
+        <v>3273397</v>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Capital Toastmasters Club</t>
+          <t>Alpha Toastmasters</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8454,8 +8454,8 @@
       <c r="S80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T80" s="9" t="n">
-        <v>0</v>
+      <c r="T80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U80" s="9" t="n">
         <v>0</v>
@@ -8466,14 +8466,14 @@
       <c r="W80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X80" s="9" t="n">
-        <v>2</v>
+      <c r="X80" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="10" t="n">
-        <v>1</v>
+      <c r="Z80" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA80" s="10" t="n">
         <v>1</v>
@@ -8491,15 +8491,15 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>1119527</v>
+        <v>503</v>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Downtown Toastmasters</t>
+          <t>Capital Toastmasters Club</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8513,17 +8513,17 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M81" s="8" t="n">
@@ -8543,7 +8543,7 @@
         <v>0</v>
       </c>
       <c r="Q81" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R81" s="9" t="n">
         <v>0</v>
@@ -8557,14 +8557,14 @@
       <c r="U81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V81" s="10" t="n">
-        <v>4</v>
+      <c r="V81" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W81" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X81" s="10" t="n">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="X81" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y81" s="9" t="n">
         <v>0</v>
@@ -8588,11 +8588,11 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>1056</v>
+        <v>1119527</v>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Ozark Orators Club</t>
+          <t>Downtown Toastmasters</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>0</v>
       </c>
       <c r="Q82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" s="9" t="n">
         <v>0</v>
@@ -8648,20 +8648,20 @@
       <c r="S82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T82" s="10" t="n">
-        <v>1</v>
+      <c r="T82" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V82" s="9" t="n">
-        <v>3</v>
+      <c r="V82" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X82" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y82" s="9" t="n">
         <v>0</v>
@@ -8681,19 +8681,19 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>9677</v>
+        <v>1056</v>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Cave Springs Toastmasters</t>
+          <t>Ozark Orators Club</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -8707,17 +8707,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M83" s="8" t="n">
@@ -8734,31 +8734,31 @@
         </is>
       </c>
       <c r="P83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q83" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R83" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V83" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X83" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y83" s="9" t="n">
         <v>0</v>
@@ -8782,15 +8782,15 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>28679535</v>
+        <v>9677</v>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>City of St. Peters Toastmasters</t>
+          <t>Cave Springs Toastmasters</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -8804,17 +8804,17 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L84" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M84" s="8" t="n">
@@ -8831,31 +8831,31 @@
         </is>
       </c>
       <c r="P84" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q84" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R84" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T84" s="9" t="n">
-        <v>0</v>
+      <c r="T84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X84" s="9" t="n">
-        <v>0</v>
+      <c r="X84" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y84" s="9" t="n">
         <v>0</v>
@@ -8879,15 +8879,15 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>4431</v>
+        <v>28679535</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Mastertoasters Club</t>
+          <t>City of St. Peters Toastmasters</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -8939,20 +8939,20 @@
       <c r="S85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T85" s="10" t="n">
-        <v>1</v>
+      <c r="T85" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X85" s="10" t="n">
-        <v>4</v>
+      <c r="X85" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y85" s="9" t="n">
         <v>0</v>
@@ -8976,15 +8976,15 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>5585</v>
+        <v>4431</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Speak Easy Toastmasters</t>
+          <t>Mastertoasters Club</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -8998,17 +8998,17 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M86" s="8" t="n">
@@ -9028,28 +9028,28 @@
         <v>1</v>
       </c>
       <c r="Q86" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S86" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T86" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X86" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y86" s="9" t="n">
         <v>0</v>
@@ -9069,19 +9069,19 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>6629</v>
+        <v>5585</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Chesterfield Toastmasters Club</t>
+          <t>Speak Easy Toastmasters</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9122,19 +9122,19 @@
         </is>
       </c>
       <c r="P87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T87" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T87" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U87" s="9" t="n">
         <v>0</v>
@@ -9145,8 +9145,8 @@
       <c r="W87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X87" s="9" t="n">
-        <v>0</v>
+      <c r="X87" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y87" s="9" t="n">
         <v>0</v>
@@ -9170,15 +9170,15 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>7746632</v>
+        <v>6629</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Rabo Masters</t>
+          <t>Chesterfield Toastmasters Club</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9230,14 +9230,14 @@
       <c r="S88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T88" s="9" t="n">
-        <v>0</v>
+      <c r="T88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -9248,8 +9248,8 @@
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="9" t="n">
-        <v>0</v>
+      <c r="Z88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA88" s="10" t="n">
         <v>1</v>
@@ -9267,15 +9267,15 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>4954048</v>
+        <v>7746632</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>RGA Toastmasters</t>
+          <t>Rabo Masters</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9289,17 +9289,17 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M89" s="8" t="n">
@@ -9327,20 +9327,20 @@
       <c r="S89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T89" s="10" t="n">
-        <v>1</v>
+      <c r="T89" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X89" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y89" s="9" t="n">
         <v>0</v>
@@ -9364,11 +9364,11 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>28676686</v>
+        <v>4954048</v>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Speak Out Pfizer (SOP)</t>
+          <t>RGA Toastmasters</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
@@ -9386,17 +9386,17 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="K90" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L90" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M90" s="8" t="n">
@@ -9424,26 +9424,26 @@
       <c r="S90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T90" s="9" t="n">
-        <v>0</v>
+      <c r="T90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X90" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" s="10" t="n">
-        <v>1</v>
+      <c r="Z90" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA90" s="10" t="n">
         <v>1</v>
@@ -9461,11 +9461,11 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>2905</v>
+        <v>28676686</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>West County Club</t>
+          <t>Speak Out Pfizer (SOP)</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
@@ -9483,10 +9483,10 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K91" s="4" t="n">
         <v>0</v>
@@ -9533,8 +9533,8 @@
       <c r="W91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X91" s="10" t="n">
-        <v>6</v>
+      <c r="X91" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y91" s="9" t="n">
         <v>0</v>
@@ -9554,19 +9554,19 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>5480999</v>
+        <v>2905</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Aetna Toastmasters</t>
+          <t>West County Club</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -9580,17 +9580,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M92" s="8" t="n">
@@ -9616,22 +9616,22 @@
         <v>0</v>
       </c>
       <c r="S92" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T92" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T92" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X92" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y92" s="9" t="n">
         <v>0</v>
@@ -9655,15 +9655,15 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>7826468</v>
+        <v>5480999</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Bayer Toastbytes</t>
+          <t>Aetna Toastmasters</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -9691,11 +9691,11 @@
         </is>
       </c>
       <c r="M93" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O93" s="7" t="inlineStr">
@@ -9713,31 +9713,31 @@
         <v>0</v>
       </c>
       <c r="S93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V93" s="9" t="n">
-        <v>0</v>
+      <c r="V93" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X93" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="X93" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA93" s="9" t="n">
-        <v>0</v>
+      <c r="Z93" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA93" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -9752,15 +9752,15 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>1267</v>
+        <v>7826468</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Creve Coeur Toastmasters</t>
+          <t>Bayer Toastbytes</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
+        <v>-14</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -9788,11 +9788,11 @@
         </is>
       </c>
       <c r="M94" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N94" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O94" s="7" t="inlineStr">
@@ -9800,8 +9800,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P94" s="10" t="n">
-        <v>4</v>
+      <c r="P94" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q94" s="9" t="n">
         <v>0</v>
@@ -9819,22 +9819,22 @@
         <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X94" s="10" t="n">
-        <v>6</v>
+      <c r="X94" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA94" s="10" t="n">
-        <v>1</v>
+      <c r="Z94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -9849,15 +9849,15 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>7866</v>
+        <v>1267</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Grace Church Toastmasters</t>
+          <t>Creve Coeur Toastmasters</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -9897,8 +9897,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P95" s="9" t="n">
-        <v>0</v>
+      <c r="P95" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q95" s="9" t="n">
         <v>0</v>
@@ -9916,19 +9916,19 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X95" s="9" t="n">
-        <v>0</v>
+      <c r="X95" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -9946,11 +9946,11 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>2075</v>
+        <v>7866</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Money Talks Club</t>
+          <t>Grace Church Toastmasters</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10018,8 +10018,8 @@
       <c r="W96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X96" s="10" t="n">
-        <v>4</v>
+      <c r="X96" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y96" s="9" t="n">
         <v>0</v>
@@ -10039,19 +10039,19 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>7715274</v>
+        <v>2075</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Centene Speaks</t>
+          <t>Money Talks Club</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10065,17 +10065,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M97" s="8" t="n">
@@ -10103,26 +10103,26 @@
       <c r="S97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T97" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U97" s="10" t="n">
-        <v>1</v>
+      <c r="T97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X97" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="10" t="n">
-        <v>1</v>
+      <c r="Z97" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -10140,15 +10140,15 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>283</v>
+        <v>7715274</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Midtown Clayton Toastmasters Club</t>
+          <t>Centene Speaks</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10162,17 +10162,17 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L98" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M98" s="8" t="n">
@@ -10200,20 +10200,20 @@
       <c r="S98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U98" s="9" t="n">
-        <v>0</v>
+      <c r="T98" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V98" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X98" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y98" s="9" t="n">
         <v>0</v>
@@ -10237,15 +10237,15 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>7724716</v>
+        <v>283</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Moneta Voices</t>
+          <t>Midtown Clayton Toastmasters Club</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10273,11 +10273,11 @@
         </is>
       </c>
       <c r="M99" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O99" s="7" t="inlineStr">
@@ -10309,17 +10309,17 @@
       <c r="W99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X99" s="9" t="n">
-        <v>0</v>
+      <c r="X99" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA99" s="9" t="n">
-        <v>0</v>
+      <c r="Z99" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA99" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -10334,15 +10334,15 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>8399</v>
+        <v>7724716</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Rent-A-Toast Club</t>
+          <t>Moneta Voices</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10356,25 +10356,25 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M100" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N100" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O100" s="7" t="inlineStr">
@@ -10383,10 +10383,10 @@
         </is>
       </c>
       <c r="P100" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q100" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R100" s="9" t="n">
         <v>0</v>
@@ -10401,22 +10401,22 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X100" s="10" t="n">
-        <v>6</v>
+      <c r="X100" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA100" s="10" t="n">
-        <v>1</v>
+      <c r="Z100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -10431,15 +10431,15 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>28675557</v>
+        <v>8399</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Sole Influencers</t>
+          <t>Rent-A-Toast Club</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10480,10 +10480,10 @@
         </is>
       </c>
       <c r="P101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" s="9" t="n">
         <v>0</v>
@@ -10498,19 +10498,19 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X101" s="9" t="n">
-        <v>1</v>
+      <c r="X101" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -10519,20 +10519,20 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>2389</v>
+        <v>28675557</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Aerospace Orators</t>
+          <t>Sole Influencers</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>0</v>
       </c>
       <c r="X102" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
@@ -10625,11 +10625,11 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>5585462</v>
+        <v>2389</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Aspiring Speakers</t>
+          <t>Aerospace Orators</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -10697,8 +10697,8 @@
       <c r="W103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X103" s="10" t="n">
-        <v>5</v>
+      <c r="X103" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y103" s="9" t="n">
         <v>0</v>
@@ -10722,15 +10722,15 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>609891</v>
+        <v>5585462</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Script Masters Club</t>
+          <t>Aspiring Speakers</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q104" s="9" t="n">
         <v>0</v>
@@ -10794,14 +10794,14 @@
       <c r="W104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X104" s="9" t="n">
-        <v>3</v>
+      <c r="X104" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="10" t="n">
-        <v>1</v>
+      <c r="Z104" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
@@ -10819,11 +10819,11 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>1491688</v>
+        <v>609891</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Shalom Church Toastmasters</t>
+          <t>Script Masters Club</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -10886,13 +10886,13 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X105" s="10" t="n">
-        <v>7</v>
+      <c r="X105" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y105" s="9" t="n">
         <v>0</v>
@@ -10916,15 +10916,15 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>3229713</v>
+        <v>1491688</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Triton Toastmasters</t>
+          <t>Shalom Church Toastmasters</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         </is>
       </c>
       <c r="P106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q106" s="9" t="n">
         <v>0</v>
@@ -10976,8 +10976,8 @@
       <c r="S106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T106" s="10" t="n">
-        <v>1</v>
+      <c r="T106" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U106" s="9" t="n">
         <v>0</v>
@@ -10989,7 +10989,7 @@
         <v>0</v>
       </c>
       <c r="X106" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
@@ -11009,15 +11009,15 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>2072</v>
+        <v>3229713</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>High-Noon Toastmasters Club</t>
+          <t>Triton Toastmasters</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11062,13 +11062,13 @@
         </is>
       </c>
       <c r="P107" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q107" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q107" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R107" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S107" s="9" t="n">
         <v>0</v>
@@ -11079,8 +11079,8 @@
       <c r="U107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V107" s="9" t="n">
-        <v>0</v>
+      <c r="V107" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -11110,15 +11110,15 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>9903</v>
+        <v>2072</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Jeffco Challengers Club</t>
+          <t>High-Noon Toastmasters Club</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11161,29 +11161,29 @@
       <c r="P108" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q108" s="9" t="n">
-        <v>0</v>
+      <c r="Q108" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T108" s="9" t="n">
-        <v>0</v>
+      <c r="T108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X108" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y108" s="9" t="n">
         <v>0</v>
@@ -11207,15 +11207,15 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>28677593</v>
+        <v>9903</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Midwest Navigators Toastmasters</t>
+          <t>Jeffco Challengers Club</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q109" s="9" t="n">
         <v>0</v>
@@ -11274,19 +11274,19 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X109" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
@@ -11304,15 +11304,15 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>1957</v>
+        <v>28677593</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>South County Toastmasters Club</t>
+          <t>Midwest Navigators Toastmasters</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11326,17 +11326,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M110" s="8" t="n">
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q110" s="9" t="n">
         <v>0</v>
@@ -11362,28 +11362,28 @@
         <v>0</v>
       </c>
       <c r="S110" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T110" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U110" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X110" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="10" t="n">
-        <v>1</v>
+      <c r="Z110" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA110" s="10" t="n">
         <v>1</v>
@@ -11401,15 +11401,15 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>461</v>
+        <v>1957</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Webster Groves Toastmasters Club</t>
+          <t>South County Toastmasters Club</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11423,17 +11423,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L111" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-12</v>
+      </c>
+      <c r="L111" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -11450,7 +11450,7 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q111" s="9" t="n">
         <v>0</v>
@@ -11459,22 +11459,22 @@
         <v>0</v>
       </c>
       <c r="S111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T111" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X111" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
@@ -11494,15 +11494,15 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>4928</v>
+        <v>461</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>F.R.B. Club</t>
+          <t>Webster Groves Toastmasters Club</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
@@ -11520,17 +11520,17 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L112" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M112" s="8" t="n">
@@ -11547,7 +11547,7 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q112" s="9" t="n">
         <v>0</v>
@@ -11565,13 +11565,13 @@
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X112" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
@@ -11595,11 +11595,11 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>28678968</v>
+        <v>4928</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Harvest Your Voice Toastmasters</t>
+          <t>F.R.B. Club</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
@@ -11617,17 +11617,17 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L113" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M113" s="8" t="n">
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q113" s="9" t="n">
         <v>0</v>
@@ -11662,7 +11662,7 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -11692,15 +11692,15 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>28679690</v>
+        <v>28678968</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Peter &amp; Paul Community Services</t>
+          <t>Harvest Your Voice Toastmasters</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q114" s="9" t="n">
         <v>0</v>
@@ -11764,14 +11764,14 @@
       <c r="W114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X114" s="9" t="n">
-        <v>0</v>
+      <c r="X114" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z114" s="9" t="n">
-        <v>0</v>
+      <c r="Z114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA114" s="10" t="n">
         <v>1</v>
@@ -11789,15 +11789,15 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>673982</v>
+        <v>28679690</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Square Talkers Toastmasters Club</t>
+          <t>Peter &amp; Paul Community Services</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -11862,13 +11862,13 @@
         <v>0</v>
       </c>
       <c r="X115" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="10" t="n">
-        <v>1</v>
+      <c r="Z115" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
@@ -11882,19 +11882,19 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>1337939</v>
+        <v>673982</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Crossroads</t>
+          <t>Square Talkers Toastmasters Club</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -11908,17 +11908,17 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L116" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L116" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M116" s="8" t="n">
@@ -11938,28 +11938,28 @@
         <v>0</v>
       </c>
       <c r="Q116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S116" s="10" t="n">
+      <c r="S116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X116" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="T116" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V116" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X116" s="10" t="n">
-        <v>6</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
@@ -11983,15 +11983,15 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>701931</v>
+        <v>1337939</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>MAC Toastmasters Club</t>
+          <t>Crossroads</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
@@ -12040,23 +12040,23 @@
       <c r="R117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V117" s="9" t="n">
-        <v>0</v>
+      <c r="S117" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T117" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U117" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V117" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X117" s="9" t="n">
-        <v>0</v>
+      <c r="X117" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
@@ -12080,15 +12080,15 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>7865</v>
+        <v>701931</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Noontime Toastmasters</t>
+          <t>MAC Toastmasters Club</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12102,17 +12102,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L118" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-4</v>
+      </c>
+      <c r="L118" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12138,7 +12138,7 @@
         <v>0</v>
       </c>
       <c r="S118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T118" s="9" t="n">
         <v>0</v>
@@ -12147,19 +12147,19 @@
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X118" s="10" t="n">
-        <v>4</v>
+      <c r="X118" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="9" t="n">
-        <v>0</v>
+      <c r="Z118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA118" s="10" t="n">
         <v>1</v>
@@ -12177,15 +12177,15 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>4590</v>
+        <v>7865</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>SPEAK UP! Club</t>
+          <t>Noontime Toastmasters</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12229,34 +12229,34 @@
         <v>0</v>
       </c>
       <c r="Q119" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S119" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T119" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T119" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V119" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X119" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z119" s="10" t="n">
-        <v>1</v>
+      <c r="Z119" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA119" s="10" t="n">
         <v>1</v>
@@ -12270,19 +12270,19 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>4908054</v>
+        <v>4590</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Central West End Toastmasters</t>
+          <t>SPEAK UP! Club</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>0</v>
       </c>
       <c r="Q120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R120" s="9" t="n">
         <v>0</v>
@@ -12334,8 +12334,8 @@
       <c r="S120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T120" s="9" t="n">
-        <v>0</v>
+      <c r="T120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U120" s="9" t="n">
         <v>0</v>
@@ -12346,14 +12346,14 @@
       <c r="W120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X120" s="9" t="n">
-        <v>3</v>
+      <c r="X120" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="9" t="n">
-        <v>0</v>
+      <c r="Z120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA120" s="10" t="n">
         <v>1</v>
@@ -12371,15 +12371,15 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>970718</v>
+        <v>4908054</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Free Speakers Toastmasters</t>
+          <t>Central West End Toastmasters</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12393,17 +12393,17 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L121" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L121" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M121" s="8" t="n">
@@ -12423,13 +12423,13 @@
         <v>0</v>
       </c>
       <c r="Q121" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S121" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T121" s="9" t="n">
         <v>0</v>
@@ -12438,19 +12438,19 @@
         <v>0</v>
       </c>
       <c r="V121" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X121" s="10" t="n">
-        <v>5</v>
+      <c r="X121" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" s="10" t="n">
-        <v>1</v>
+      <c r="Z121" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA121" s="10" t="n">
         <v>1</v>
@@ -12468,11 +12468,11 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>5000</v>
+        <v>970718</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Grand Center Club</t>
+          <t>Free Speakers Toastmasters</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -12520,13 +12520,13 @@
         <v>0</v>
       </c>
       <c r="Q122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T122" s="9" t="n">
         <v>0</v>
@@ -12535,13 +12535,13 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X122" s="9" t="n">
-        <v>3</v>
+      <c r="X122" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
@@ -12565,11 +12565,11 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>2187152</v>
+        <v>5000</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Jacobs P3</t>
+          <t>Grand Center Club</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
@@ -12587,17 +12587,17 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L123" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M123" s="8" t="n">
@@ -12637,8 +12637,8 @@
       <c r="W123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X123" s="10" t="n">
-        <v>5</v>
+      <c r="X123" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
@@ -12662,11 +12662,11 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>1254245</v>
+        <v>2187152</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>MilliporeSigma Toastmasters</t>
+          <t>Jacobs P3</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
@@ -12684,17 +12684,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M124" s="8" t="n">
@@ -12734,8 +12734,8 @@
       <c r="W124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X124" s="9" t="n">
-        <v>3</v>
+      <c r="X124" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
@@ -12755,15 +12755,15 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>4345</v>
+        <v>1254245</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Anheuser-Busch Toastmasters Club</t>
+          <t>MilliporeSigma Toastmasters</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
@@ -12781,13 +12781,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>0</v>
       </c>
       <c r="X125" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
@@ -12856,15 +12856,15 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>4115</v>
+        <v>4345</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Smedley Hometown Memorial Toastmasters Club</t>
+          <t>Anheuser-Busch Toastmasters Club</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -12934,8 +12934,8 @@
       <c r="Y126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z126" s="9" t="n">
-        <v>0</v>
+      <c r="Z126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA126" s="10" t="n">
         <v>1</v>
@@ -12953,15 +12953,15 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>532</v>
+        <v>4115</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Tarsus Toastmasters</t>
+          <t>Smedley Hometown Memorial Toastmasters Club</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13026,13 +13026,13 @@
         <v>0</v>
       </c>
       <c r="X127" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z127" s="10" t="n">
-        <v>1</v>
+      <c r="Z127" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA127" s="10" t="n">
         <v>1</v>
@@ -13050,15 +13050,15 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>3913401</v>
+        <v>532</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Toast of WU</t>
+          <t>Tarsus Toastmasters</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13072,17 +13072,17 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L128" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L128" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M128" s="8" t="n">
@@ -13099,7 +13099,7 @@
         </is>
       </c>
       <c r="P128" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q128" s="9" t="n">
         <v>0</v>
@@ -13110,20 +13110,20 @@
       <c r="S128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T128" s="10" t="n">
-        <v>1</v>
+      <c r="T128" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X128" s="10" t="n">
-        <v>4</v>
+      <c r="X128" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
@@ -13147,11 +13147,11 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>28675986</v>
+        <v>3913401</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Writers Ink Toastmasters Club</t>
+          <t>Toast of WU</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
@@ -13169,17 +13169,17 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L129" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M129" s="8" t="n">
@@ -13196,44 +13196,141 @@
         </is>
       </c>
       <c r="P129" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X129" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA129" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="n">
+        <v>28675986</v>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>Writers Ink Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F130" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G130" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I130" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J130" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="K130" s="4" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L130" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M130" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N130" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O130" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P130" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q129" s="10" t="n">
+      <c r="Q130" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R129" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S129" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T129" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U129" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X129" s="10" t="n">
+      <c r="R130" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S130" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T130" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U130" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X130" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="Y129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA129" s="10" t="n">
+      <c r="Y130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA130" s="10" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA129"/>
+  <autoFilter ref="A1:AA130"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13401,7 +13498,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -13452,7 +13549,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -13518,7 +13615,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -13533,7 +13630,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -13551,7 +13648,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -13599,7 +13696,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -13665,7 +13762,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -13698,7 +13795,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13713,25 +13810,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -13797,7 +13894,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -13863,7 +13960,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -13896,7 +13993,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -13947,7 +14044,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -13962,7 +14059,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -13995,7 +14092,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -14013,7 +14110,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14094,7 +14191,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -14112,13 +14209,13 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -14160,7 +14257,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -14178,7 +14275,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -14193,7 +14290,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/211/inyear.xlsx
+++ b/docs/d/211/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/211/inyear.xlsx
+++ b/docs/d/211/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/211/inyear.xlsx
+++ b/docs/d/211/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/211/inyear.xlsx
+++ b/docs/d/211/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/211/inyear.xlsx
+++ b/docs/d/211/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 36 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 36 clubs short</t>
         </is>
       </c>
     </row>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -3992,8 +3992,8 @@
       <c r="S34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T34" s="9" t="n">
-        <v>0</v>
+      <c r="T34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U34" s="9" t="n">
         <v>0</v>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="P36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q36" s="9" t="n">
         <v>0</v>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>1</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>0</v>
       </c>
       <c r="S79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T79" s="10" t="n">
         <v>1</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8639,8 +8639,8 @@
       <c r="P82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" s="9" t="n">
-        <v>1</v>
+      <c r="Q82" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R82" s="9" t="n">
         <v>0</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>0</v>
       </c>
       <c r="X98" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y98" s="9" t="n">
         <v>0</v>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-12</v>
+        <v>-6</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -11467,11 +11467,11 @@
       <c r="U111" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V111" s="9" t="n">
-        <v>3</v>
+      <c r="V111" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X111" s="10" t="n">
         <v>5</v>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11655,8 +11655,8 @@
       <c r="S113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T113" s="9" t="n">
-        <v>0</v>
+      <c r="T113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U113" s="9" t="n">
         <v>0</v>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-21</v>
+        <v>-16</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13169,17 +13169,17 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L129" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L129" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M129" s="8" t="n">
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>1</v>
       </c>
       <c r="V130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
@@ -13615,7 +13615,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -13945,7 +13945,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14143,7 +14143,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14176,7 +14176,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -14290,7 +14290,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/211/inyear.xlsx
+++ b/docs/d/211/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 10 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 10 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 36 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 36 clubs short</t>
         </is>
       </c>
     </row>
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
         <v>1</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="9" t="n">
         <v>0</v>
@@ -2052,8 +2052,8 @@
       <c r="S14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T14" s="9" t="n">
-        <v>0</v>
+      <c r="T14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U14" s="9" t="n">
         <v>0</v>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>0</v>
@@ -4475,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T39" s="9" t="n">
         <v>0</v>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="P47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q47" s="9" t="n">
         <v>0</v>
@@ -5509,10 +5509,10 @@
         <v>10</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="P56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q56" s="9" t="n">
         <v>0</v>
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6223,8 +6223,8 @@
       <c r="S57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T57" s="9" t="n">
-        <v>0</v>
+      <c r="T57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U57" s="9" t="n">
         <v>0</v>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K68" s="4" t="n">
         <v>-3</v>
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -7767,7 +7767,7 @@
         <v>0</v>
       </c>
       <c r="Q73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" s="9" t="n">
         <v>0</v>
@@ -7775,8 +7775,8 @@
       <c r="S73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T73" s="9" t="n">
-        <v>0</v>
+      <c r="T73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U73" s="9" t="n">
         <v>0</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>3</v>
       </c>
       <c r="Q111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R111" s="9" t="n">
         <v>0</v>
@@ -11523,10 +11523,10 @@
         <v>12</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -11617,17 +11617,17 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L113" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L113" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M113" s="8" t="n">
@@ -11662,7 +11662,7 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>0</v>
       </c>
       <c r="V119" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
@@ -12517,7 +12517,7 @@
         </is>
       </c>
       <c r="P122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q122" s="9" t="n">
         <v>1</v>
@@ -12590,10 +12590,10 @@
         <v>12</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -13780,7 +13780,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13879,7 +13879,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14191,7 +14191,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
